--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753879301_individual_h_11.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753879301_individual_h_11.xlsx
@@ -658,7 +658,7 @@
         <v>0.008524561436371531</v>
       </c>
       <c r="C2" t="n">
-        <v>69442758</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>69442758</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>47805877</v>
+        <v>3991012</v>
       </c>
       <c r="L2" t="n">
-        <v>25248806</v>
+        <v>1652870</v>
       </c>
       <c r="M2" t="n">
-        <v>5840017</v>
+        <v>298524</v>
       </c>
       <c r="N2" t="n">
-        <v>253877</v>
+        <v>6737</v>
       </c>
       <c r="O2" t="n">
-        <v>3420081</v>
+        <v>168714</v>
       </c>
       <c r="P2" t="n">
-        <v>1320925</v>
+        <v>58269</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999855160713196</v>
+        <v>0.9999572038650513</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8335389494895935</v>
+        <v>0.7150097489356995</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7040111422538757</v>
+        <v>0.534562349319458</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6335808038711548</v>
+        <v>0.4021364748477936</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2280650585889816</v>
+        <v>0.05365220457315445</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6862678527832031</v>
+        <v>0.4485690593719482</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8003331422805786</v>
+        <v>0.5912153124809265</v>
       </c>
       <c r="X2" t="n">
-        <v>69442758</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>69442758</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>52683690</v>
+        <v>4734132</v>
       </c>
       <c r="AG2" t="n">
-        <v>32880041</v>
+        <v>3030830</v>
       </c>
       <c r="AH2" t="n">
-        <v>8825327</v>
+        <v>808192</v>
       </c>
       <c r="AI2" t="n">
-        <v>650092</v>
+        <v>59360</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5059340</v>
+        <v>461747</v>
       </c>
       <c r="AK2" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9558059573173523</v>
+        <v>0.9544405341148376</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9118016958236694</v>
+        <v>0.9131393432617188</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582155108451843</v>
+        <v>0.8580844402313232</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6616813540458679</v>
+        <v>0.660965621471405</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020092487335205</v>
+        <v>0.902009904384613</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314546585083008</v>
+        <v>0.9314878582954407</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.00204248073217291</v>
       </c>
       <c r="C3" t="n">
-        <v>174</v>
+        <v>47</v>
       </c>
       <c r="D3" t="n">
-        <v>47805877</v>
+        <v>3991012</v>
       </c>
       <c r="E3" t="n">
-        <v>6979271</v>
+        <v>904979</v>
       </c>
       <c r="F3" t="n">
-        <v>201719</v>
+        <v>39902</v>
       </c>
       <c r="G3" t="n">
-        <v>17900</v>
+        <v>3724</v>
       </c>
       <c r="H3" t="n">
-        <v>13532</v>
+        <v>3835</v>
       </c>
       <c r="I3" t="n">
-        <v>1223</v>
+        <v>457</v>
       </c>
       <c r="J3" t="n">
-        <v>110181835</v>
+        <v>10016352</v>
       </c>
       <c r="K3" t="n">
-        <v>115058879</v>
+        <v>9794897</v>
       </c>
       <c r="L3" t="n">
-        <v>132868358</v>
+        <v>11557949</v>
       </c>
       <c r="M3" t="n">
-        <v>165951830</v>
+        <v>14942023</v>
       </c>
       <c r="N3" t="n">
-        <v>177782775</v>
+        <v>16120809</v>
       </c>
       <c r="O3" t="n">
-        <v>172449153</v>
+        <v>15609695</v>
       </c>
       <c r="P3" t="n">
-        <v>177167511</v>
+        <v>16095379</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8688865900039673</v>
+        <v>0.8072507381439209</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6986033320426941</v>
+        <v>0.4959827661514282</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5671951770782471</v>
+        <v>0.3163148164749146</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2581299543380737</v>
+        <v>0.07488884031772614</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6093215346336365</v>
+        <v>0.3291961252689362</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6205765008926392</v>
+        <v>0.3004609942436218</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>52683690</v>
+        <v>4734132</v>
       </c>
       <c r="Z3" t="n">
-        <v>2167250</v>
+        <v>194580</v>
       </c>
       <c r="AA3" t="n">
-        <v>93227</v>
+        <v>8401</v>
       </c>
       <c r="AB3" t="n">
-        <v>74908</v>
+        <v>6802</v>
       </c>
       <c r="AC3" t="n">
-        <v>291</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>330</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>110182842</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>122169944</v>
+        <v>11159664</v>
       </c>
       <c r="AG3" t="n">
-        <v>140303288</v>
+        <v>12708783</v>
       </c>
       <c r="AH3" t="n">
-        <v>167871272</v>
+        <v>15252180</v>
       </c>
       <c r="AI3" t="n">
-        <v>178309683</v>
+        <v>16209192</v>
       </c>
       <c r="AJ3" t="n">
-        <v>173463040</v>
+        <v>15766935</v>
       </c>
       <c r="AK3" t="n">
-        <v>177351199</v>
+        <v>16122390</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.957542359828949</v>
+        <v>0.9575594663619995</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097501635551453</v>
+        <v>0.9094722867012024</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.857134997844696</v>
+        <v>0.8563569188117981</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6609823703765869</v>
+        <v>0.6598488092422485</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013718962669373</v>
+        <v>0.9009644985198975</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311618804931641</v>
+        <v>0.9308778047561646</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03218358813514684</v>
       </c>
       <c r="C4" t="n">
-        <v>141</v>
+        <v>44</v>
       </c>
       <c r="D4" t="n">
-        <v>8785772</v>
+        <v>1417969</v>
       </c>
       <c r="E4" t="n">
-        <v>25248806</v>
+        <v>1652870</v>
       </c>
       <c r="F4" t="n">
-        <v>1777399</v>
+        <v>203030</v>
       </c>
       <c r="G4" t="n">
-        <v>116257</v>
+        <v>20168</v>
       </c>
       <c r="H4" t="n">
-        <v>194022</v>
+        <v>34153</v>
       </c>
       <c r="I4" t="n">
-        <v>19438</v>
+        <v>4281</v>
       </c>
       <c r="J4" t="n">
-        <v>1007</v>
+        <v>270</v>
       </c>
       <c r="K4" t="n">
-        <v>9547025</v>
+        <v>1590747</v>
       </c>
       <c r="L4" t="n">
-        <v>10615407</v>
+        <v>1439136</v>
       </c>
       <c r="M4" t="n">
-        <v>3377461</v>
+        <v>443821</v>
       </c>
       <c r="N4" t="n">
-        <v>859301</v>
+        <v>118831</v>
       </c>
       <c r="O4" t="n">
-        <v>1563514</v>
+        <v>207402</v>
       </c>
       <c r="P4" t="n">
-        <v>329544</v>
+        <v>40289</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999927878379822</v>
+        <v>0.9999786019325256</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8508458137512207</v>
+        <v>0.7583355903625488</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7012968063354492</v>
+        <v>0.5145503878593445</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5985528826713562</v>
+        <v>0.3540997803211212</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2421679347753525</v>
+        <v>0.0625162348151207</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6455097198486328</v>
+        <v>0.3797218203544617</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6990845203399658</v>
+        <v>0.3984341621398926</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2275167</v>
+        <v>211204</v>
       </c>
       <c r="Z4" t="n">
-        <v>32880041</v>
+        <v>3030830</v>
       </c>
       <c r="AA4" t="n">
-        <v>912484</v>
+        <v>83661</v>
       </c>
       <c r="AB4" t="n">
-        <v>60883</v>
+        <v>5621</v>
       </c>
       <c r="AC4" t="n">
-        <v>12512</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>748</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2435960</v>
+        <v>225980</v>
       </c>
       <c r="AG4" t="n">
-        <v>3180477</v>
+        <v>288302</v>
       </c>
       <c r="AH4" t="n">
-        <v>1458019</v>
+        <v>133664</v>
       </c>
       <c r="AI4" t="n">
-        <v>332393</v>
+        <v>30448</v>
       </c>
       <c r="AJ4" t="n">
-        <v>549627</v>
+        <v>50162</v>
       </c>
       <c r="AK4" t="n">
-        <v>145856</v>
+        <v>13278</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9566733241081238</v>
+        <v>0.9559974670410156</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910774827003479</v>
+        <v>0.9113021492958069</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576748967170715</v>
+        <v>0.8572198748588562</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6613316535949707</v>
+        <v>0.660406768321991</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016904234886169</v>
+        <v>0.9014868140220642</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313082695007324</v>
+        <v>0.9311826825141907</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="D5" t="n">
-        <v>542952</v>
+        <v>127399</v>
       </c>
       <c r="E5" t="n">
-        <v>2914250</v>
+        <v>397075</v>
       </c>
       <c r="F5" t="n">
-        <v>5840017</v>
+        <v>298524</v>
       </c>
       <c r="G5" t="n">
-        <v>268581</v>
+        <v>33123</v>
       </c>
       <c r="H5" t="n">
-        <v>659437</v>
+        <v>76010</v>
       </c>
       <c r="I5" t="n">
-        <v>70942</v>
+        <v>11575</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7213819</v>
+        <v>952944</v>
       </c>
       <c r="L5" t="n">
-        <v>10893029</v>
+        <v>1679645</v>
       </c>
       <c r="M5" t="n">
-        <v>4456292</v>
+        <v>645232</v>
       </c>
       <c r="N5" t="n">
-        <v>729647</v>
+        <v>83223</v>
       </c>
       <c r="O5" t="n">
-        <v>2192852</v>
+        <v>343789</v>
       </c>
       <c r="P5" t="n">
-        <v>807620</v>
+        <v>135663</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999943971633911</v>
+        <v>0.9999834895133972</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9066901206970215</v>
+        <v>0.844228208065033</v>
       </c>
       <c r="S5" t="n">
-        <v>0.88025963306427</v>
+        <v>0.8090105652809143</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9563884139060974</v>
+        <v>0.9333080649375916</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9911541342735291</v>
+        <v>0.9876264929771423</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9790878295898438</v>
+        <v>0.9662458896636963</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9936692714691162</v>
+        <v>0.9892249703407288</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>88591</v>
+        <v>8137</v>
       </c>
       <c r="Z5" t="n">
-        <v>944516</v>
+        <v>87456</v>
       </c>
       <c r="AA5" t="n">
-        <v>8825327</v>
+        <v>808192</v>
       </c>
       <c r="AB5" t="n">
-        <v>109796</v>
+        <v>10038</v>
       </c>
       <c r="AC5" t="n">
-        <v>321116</v>
+        <v>29300</v>
       </c>
       <c r="AD5" t="n">
-        <v>6963</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2336006</v>
+        <v>209824</v>
       </c>
       <c r="AG5" t="n">
-        <v>3261794</v>
+        <v>301685</v>
       </c>
       <c r="AH5" t="n">
-        <v>1470982</v>
+        <v>135564</v>
       </c>
       <c r="AI5" t="n">
-        <v>333432</v>
+        <v>30600</v>
       </c>
       <c r="AJ5" t="n">
-        <v>553593</v>
+        <v>50756</v>
       </c>
       <c r="AK5" t="n">
-        <v>146525</v>
+        <v>13405</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973433792591095</v>
+        <v>0.9733120203018188</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641349911689758</v>
+        <v>0.963870108127594</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9836938381195068</v>
+        <v>0.9835128784179688</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962932467460632</v>
+        <v>0.9962615370750427</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938582181930542</v>
+        <v>0.9938199520111084</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983722567558289</v>
+        <v>0.9983659982681274</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="D6" t="n">
-        <v>160254</v>
+        <v>24147</v>
       </c>
       <c r="E6" t="n">
-        <v>237957</v>
+        <v>26283</v>
       </c>
       <c r="F6" t="n">
-        <v>230203</v>
+        <v>23354</v>
       </c>
       <c r="G6" t="n">
-        <v>253877</v>
+        <v>6737</v>
       </c>
       <c r="H6" t="n">
-        <v>91297</v>
+        <v>8259</v>
       </c>
       <c r="I6" t="n">
-        <v>9792</v>
+        <v>1151</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>71687</v>
+        <v>6603</v>
       </c>
       <c r="Z6" t="n">
-        <v>58910</v>
+        <v>5375</v>
       </c>
       <c r="AA6" t="n">
-        <v>120587</v>
+        <v>11116</v>
       </c>
       <c r="AB6" t="n">
-        <v>650092</v>
+        <v>59360</v>
       </c>
       <c r="AC6" t="n">
-        <v>76956</v>
+        <v>7024</v>
       </c>
       <c r="AD6" t="n">
-        <v>5292</v>
+        <v>482</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="D7" t="n">
-        <v>54284</v>
+        <v>19492</v>
       </c>
       <c r="E7" t="n">
-        <v>440831</v>
+        <v>98903</v>
       </c>
       <c r="F7" t="n">
-        <v>1067560</v>
+        <v>152292</v>
       </c>
       <c r="G7" t="n">
-        <v>401936</v>
+        <v>50246</v>
       </c>
       <c r="H7" t="n">
-        <v>3420081</v>
+        <v>168714</v>
       </c>
       <c r="I7" t="n">
-        <v>228149</v>
+        <v>22825</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>207</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8910</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>328074</v>
+        <v>30153</v>
       </c>
       <c r="AB7" t="n">
-        <v>83879</v>
+        <v>7720</v>
       </c>
       <c r="AC7" t="n">
-        <v>5059340</v>
+        <v>461747</v>
       </c>
       <c r="AD7" t="n">
-        <v>132523</v>
+        <v>12065</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>326</v>
+        <v>69</v>
       </c>
       <c r="D8" t="n">
-        <v>3763</v>
+        <v>1740</v>
       </c>
       <c r="E8" t="n">
-        <v>43098</v>
+        <v>11896</v>
       </c>
       <c r="F8" t="n">
-        <v>100580</v>
+        <v>25243</v>
       </c>
       <c r="G8" t="n">
-        <v>54627</v>
+        <v>11570</v>
       </c>
       <c r="H8" t="n">
-        <v>605226</v>
+        <v>85145</v>
       </c>
       <c r="I8" t="n">
-        <v>1320925</v>
+        <v>58269</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>308</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>891</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3647</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2927</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>138752</v>
+        <v>12696</v>
       </c>
       <c r="AD8" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
